--- a/feedback_surveys/022_livestock_feed_supplier_quality_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/022_livestock_feed_supplier_quality_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>customer_service</t>
+          <t>customer_service_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Customer Service 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>contact_info_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Contact Info 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>shipping_cost</t>
+          <t>shipping_cost_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shipping Cost</t>
+          <t>Shipping Cost 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1165,46 +1165,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>supplier_rating_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>supplier_rating_choices</t>
+          <t>customer_support_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1233,46 +1233,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_support_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_support_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1301,46 +1301,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>delivery_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>On time</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>delivery_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -1352,46 +1352,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>on_time</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>On time</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>delivery_choices</t>
+          <t>product_availability_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>delivery_choices</t>
+          <t>product_availability_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mostly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mostly</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Always</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1420,121 +1420,121 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mostly</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mostly</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>product_availability_choices</t>
+          <t>customer_service_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>responsive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Responsive</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>product_availability_choices</t>
+          <t>customer_service_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>non_responsive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Non Responsive</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>issue_resolution_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>responsive</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>customer_service_choices</t>
+          <t>issue_resolution_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>non_responsive</t>
+          <t>not_resolved</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Non Responsive</t>
+          <t>Not Resolved</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>issue_resolution_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>issue_resolution_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>not_resolved</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not Resolved</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>contact_info_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>contact_person_choices</t>
+          <t>contact_info_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,66 +1568,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>shipping_cost_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>shipping_cost_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>not_available</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>Not Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>shipping_cost_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>shipping_cost_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>High</t>
         </is>
